--- a/iCare_Virtual_Hospital_Project_Status.xlsx
+++ b/iCare_Virtual_Hospital_Project_Status.xlsx
@@ -183,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -205,11 +205,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -295,6 +339,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -660,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -703,6 +749,10 @@
           <t xml:space="preserve">  Doctor Account  (25 items)</t>
         </is>
       </c>
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="29" t="n"/>
+      <c r="D2" s="29" t="n"/>
+      <c r="E2" s="30" t="n"/>
     </row>
     <row r="3" ht="35" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -1335,6 +1385,10 @@
           <t xml:space="preserve">  Patient Account  (13 items)</t>
         </is>
       </c>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="30" t="n"/>
     </row>
     <row r="29" ht="35" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1667,6 +1721,10 @@
           <t xml:space="preserve">  Home Page  (27 items)</t>
         </is>
       </c>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="30" t="n"/>
     </row>
     <row r="43" ht="35" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -2349,6 +2407,10 @@
           <t xml:space="preserve">  Video Consultation  (5 items)</t>
         </is>
       </c>
+      <c r="B70" s="29" t="n"/>
+      <c r="C70" s="29" t="n"/>
+      <c r="D70" s="29" t="n"/>
+      <c r="E70" s="30" t="n"/>
     </row>
     <row r="71" ht="35" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -2481,6 +2543,10 @@
           <t xml:space="preserve">  Prescription Management  (6 items)</t>
         </is>
       </c>
+      <c r="B76" s="29" t="n"/>
+      <c r="C76" s="29" t="n"/>
+      <c r="D76" s="29" t="n"/>
+      <c r="E76" s="30" t="n"/>
     </row>
     <row r="77" ht="35" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -2638,6 +2704,10 @@
           <t xml:space="preserve">  Health Tracker  (13 items)</t>
         </is>
       </c>
+      <c r="B83" s="29" t="n"/>
+      <c r="C83" s="29" t="n"/>
+      <c r="D83" s="29" t="n"/>
+      <c r="E83" s="30" t="n"/>
     </row>
     <row r="84" ht="35" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -2970,6 +3040,10 @@
           <t xml:space="preserve">  Pharmacy Account  (27 items)</t>
         </is>
       </c>
+      <c r="B97" s="29" t="n"/>
+      <c r="C97" s="29" t="n"/>
+      <c r="D97" s="29" t="n"/>
+      <c r="E97" s="30" t="n"/>
     </row>
     <row r="98" ht="35" customHeight="1">
       <c r="A98" s="6" t="n">
@@ -3652,6 +3726,10 @@
           <t xml:space="preserve">  Laboratory Account  (30 items)</t>
         </is>
       </c>
+      <c r="B125" s="29" t="n"/>
+      <c r="C125" s="29" t="n"/>
+      <c r="D125" s="29" t="n"/>
+      <c r="E125" s="30" t="n"/>
     </row>
     <row r="126" ht="35" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -4409,6 +4487,10 @@
           <t xml:space="preserve">  LMS  (7 items)</t>
         </is>
       </c>
+      <c r="B156" s="29" t="n"/>
+      <c r="C156" s="29" t="n"/>
+      <c r="D156" s="29" t="n"/>
+      <c r="E156" s="30" t="n"/>
     </row>
     <row r="157" ht="35" customHeight="1">
       <c r="A157" s="3" t="n">
@@ -4591,6 +4673,10 @@
           <t xml:space="preserve">  Registration / Sign-up  (9 items)</t>
         </is>
       </c>
+      <c r="B164" s="29" t="n"/>
+      <c r="C164" s="29" t="n"/>
+      <c r="D164" s="29" t="n"/>
+      <c r="E164" s="30" t="n"/>
     </row>
     <row r="165" ht="35" customHeight="1">
       <c r="A165" s="6" t="n">
@@ -4823,6 +4909,10 @@
           <t xml:space="preserve">  General / Cross-cutting  (15 items)</t>
         </is>
       </c>
+      <c r="B174" s="29" t="n"/>
+      <c r="C174" s="29" t="n"/>
+      <c r="D174" s="29" t="n"/>
+      <c r="E174" s="30" t="n"/>
     </row>
     <row r="175" ht="35" customHeight="1">
       <c r="A175" s="3" t="n">
@@ -5199,8 +5289,65 @@
         </is>
       </c>
     </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Newly Added Completed  (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="35" customHeight="1">
+      <c r="A192" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Doctor Account</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>Doctor Signup page: Hours selection UI improved</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="35" customHeight="1">
+      <c r="A193" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Registration / Sign-up</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Valid Email and Valid Phone Number validation on submission</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A156:E156"/>
     <mergeCell ref="A125:E125"/>
@@ -5209,6 +5356,7 @@
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A174:E174"/>
+    <mergeCell ref="A191:E191"/>
     <mergeCell ref="A164:E164"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A70:E70"/>
@@ -5223,7 +5371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5272,6 +5420,11 @@
           <t xml:space="preserve">  Doctor Account  (8 items)</t>
         </is>
       </c>
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="29" t="n"/>
+      <c r="D2" s="29" t="n"/>
+      <c r="E2" s="29" t="n"/>
+      <c r="F2" s="30" t="n"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -5519,6 +5672,11 @@
           <t xml:space="preserve">  Patient Account  (8 items)</t>
         </is>
       </c>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="30" t="n"/>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -5766,6 +5924,11 @@
           <t xml:space="preserve">  Video Consultation  (1 items)</t>
         </is>
       </c>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -5803,6 +5966,11 @@
           <t xml:space="preserve">  Pharmacy Account  (6 items)</t>
         </is>
       </c>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
     </row>
     <row r="23" ht="38" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -5990,6 +6158,11 @@
           <t xml:space="preserve">  Laboratory Account  (11 items)</t>
         </is>
       </c>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
     </row>
     <row r="30" ht="38" customHeight="1">
       <c r="A30" s="6" t="n">
@@ -6327,6 +6500,11 @@
           <t xml:space="preserve">  LMS  (17 items)</t>
         </is>
       </c>
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="30" t="n"/>
     </row>
     <row r="42" ht="38" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -6844,6 +7022,11 @@
           <t xml:space="preserve">  Registration / Sign-up  (3 items)</t>
         </is>
       </c>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="29" t="n"/>
+      <c r="D59" s="29" t="n"/>
+      <c r="E59" s="29" t="n"/>
+      <c r="F59" s="30" t="n"/>
     </row>
     <row r="60" ht="38" customHeight="1">
       <c r="A60" s="6" t="n">
@@ -6941,6 +7124,11 @@
           <t xml:space="preserve">  Technical / Backend  (12 items)</t>
         </is>
       </c>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="30" t="n"/>
     </row>
     <row r="64" ht="38" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -7308,6 +7496,11 @@
           <t xml:space="preserve">  Admin Panel  (3 items)</t>
         </is>
       </c>
+      <c r="B76" s="29" t="n"/>
+      <c r="C76" s="29" t="n"/>
+      <c r="D76" s="29" t="n"/>
+      <c r="E76" s="29" t="n"/>
+      <c r="F76" s="30" t="n"/>
     </row>
     <row r="77" ht="38" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -7405,6 +7598,11 @@
           <t xml:space="preserve">  General / Cross-cutting  (8 items)</t>
         </is>
       </c>
+      <c r="B80" s="29" t="n"/>
+      <c r="C80" s="29" t="n"/>
+      <c r="D80" s="29" t="n"/>
+      <c r="E80" s="29" t="n"/>
+      <c r="F80" s="30" t="n"/>
     </row>
     <row r="81" ht="38" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -7646,13 +7844,291 @@
         </is>
       </c>
     </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Newly Added Tasks  (9 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="38" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Login / Signup</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Login page: Signup modal not working — replace with link text to patient signup page</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="38" customHeight="1">
+      <c r="A92" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>When logged in as Admin, 'Add Doctor / etc.' button hides behind WhatsApp icon</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="38" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Admin approval cards don't show doctor details (qualification, etc.)</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="38" customHeight="1">
+      <c r="A94" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Admin dashboard 'Add New Doctor' not working</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="38" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Admin panel 'Verify Doctors' — data not showing</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="38" customHeight="1">
+      <c r="A96" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>No option to manage Doctors and other user types</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="38" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Admin Panel</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Users Deactivate option missing</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="38" customHeight="1">
+      <c r="A98" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Account</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Signup: Specialist and Degree dropdown missing</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="38" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>General / Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Website open URL should default to Home page</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A20:F20"/>
@@ -7700,7 +8176,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
@@ -7710,7 +8186,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -7720,7 +8196,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -7731,7 +8207,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
